--- a/data/trans_orig/IP31KM03_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM03_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31401</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27397</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33971</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>41501</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37372</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43854</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41200</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>79213</t>
+          <t>69519</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73224</t>
+          <t>64500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83274</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6034</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10038</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4994</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9123</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>136584</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>128712</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>143403</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,96%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>136097</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127351</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>142701</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,44%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,94%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>125998</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150663</t>
+          <t>118741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165813</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>294848</t>
+          <t>262582</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>283380</t>
+          <t>252811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>305327</t>
+          <t>270955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13639</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28330</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23202</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16598</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31948</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>26777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>46411</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57879</t>
+          <t>49749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>170545</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>160459</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>178283</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>80,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>150633</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>142768</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>158188</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>181397</t>
+          <t>151622</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170954</t>
+          <t>142198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189698</t>
+          <t>158407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>332032</t>
+          <t>322167</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318870</t>
+          <t>309448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343339</t>
+          <t>332274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29581</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21843</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39667</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22439</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14884</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30304</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31093</t>
+          <t>23050</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41536</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>52631</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>42524</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66693</t>
+          <t>65350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>235192</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>220639</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>247923</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>80,48%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,5%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>84,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>225272</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>212704</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>241129</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>246193</t>
+          <t>204004</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>230734</t>
+          <t>193989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259923</t>
+          <t>215393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>471465</t>
+          <t>439196</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>452625</t>
+          <t>420349</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492566</t>
+          <t>454956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57029</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44298</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>71582</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,52%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>48995</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33138</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61563</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58806</t>
+          <t>51333</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>61348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>107801</t>
+          <t>108362</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126641</t>
+          <t>127209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>573722</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>554146</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>590560</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>553504</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>535855</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>570235</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>84,75%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>82,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602396</t>
+          <t>504214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>642254</t>
+          <t>534529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1151284</t>
+          <t>1070568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1203148</t>
+          <t>1117360</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>113102</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>96264</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>132678</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>99630</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>82899</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117279</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>83679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142337</t>
+          <t>113994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>220309</t>
+          <t>211568</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194719</t>
+          <t>187671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246583</t>
+          <t>234463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
